--- a/Nhom01/SE_9/SE_9_Nhom01_AsisScenario.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_AsisScenario.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Describe current manual work including Excel and paper receipts; each step has actor, tool, input, output and pain.</t>
+          <t>Tài liệu mô tả công việc thủ công hiện tại, gồm Excel và chứng từ giấy; mỗi bước nêu người thực hiện, công cụ, đầu vào, đầu ra và vấn đề gặp phải.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 3–10, B:G</t>
+          <t>AS-001–AS-008</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Pains cover fee collection and resident records, including authority reporting.</t>
+          <t>Các vấn đề bao quát việc thu phí, hồ sơ cư dân và báo cáo cho cơ quan chức năng.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Rows 5, 7–10</t>
+          <t>AS-001–AS-008</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Each pain cites checkable evidence and links to a wish.</t>
+          <t>Mỗi vấn đề hiện trạng có bằng chứng kiểm tra được và liên kết tới một mong muốn.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rows 3–10; không có cột nguồn hoặc RAW ID</t>
+          <t>AS-001–AS-008; RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>As-Is is wider than the wish list and includes current facts the client did not ask to change.</t>
+          <t>Kịch bản hiện trạng rộng hơn danh sách mong muốn, có cả những dữ kiện khách hàng chưa yêu cầu thay đổi.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Rows 3–10; đối chiếu Wish List</t>
+          <t>AS-001–AS-008; RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Unconfirmed pains are labelled; confirmed pains name the confirmer.</t>
+          <t>Vấn đề chưa được khách hàng xác nhận phải được đánh dấu; vấn đề đã xác nhận phải ghi người xác nhận.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Rows 3–10</t>
+          <t>AS-001–AS-008</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
